--- a/generated_models/HDFCBANK_model_20260222.xlsx
+++ b/generated_models/HDFCBANK_model_20260222.xlsx
@@ -8,21 +8,12 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PnL" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Advances Mix" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Advances Build" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deposit Schedule" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NDTL" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GNPA Schedule" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ROE Tree" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regulatory Ratios" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Valuation" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Football Field" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Beta" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Peer Comps" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Thesis" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P&amp;L" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Valuation" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Thesis" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Key Metrics" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -32,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,7 +33,37 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="20"/>
+      <color rgb="001F4E79"/>
+      <sz val="24"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <color rgb="00666666"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00999999"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="002F5496"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00666666"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FF9900"/>
+      <sz val="14"/>
     </font>
     <font>
       <b val="1"/>
@@ -50,25 +71,51 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00000000"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0000AA00"/>
     </font>
     <font>
       <b val="1"/>
       <sz val="12"/>
     </font>
-    <font>
-      <b val="1"/>
-      <sz val="16"/>
-    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+        <bgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -76,20 +123,60 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -458,282 +545,186 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="80" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Financial Model - HDFC Bank Ltd</t>
+          <t>FINANCIAL MODEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>HDFC Bank Ltd</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Ticker: HDFCBANK</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Date Generated: 22 February 2026</t>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Ticker: HDFCBANK | NSE: HDFCBANK</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Analyst:</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Generated: 22 February 2026</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Recommendation:</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>TBD</t>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>KEY DATA</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Target Price:</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0</v>
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Upside/Downside:</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Bank</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Market Cap</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>₹1,407,837 Cr</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Thesis Summary:</t>
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Current Price</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>₹1,851.85</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Model generated by Mosaic AI</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>ROE DuPont Decomposition</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Regulatory Ratios</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Valuation</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>A) RESIDUAL INCOME VALUATION (RIV)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Cost of Equity (Ke)</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Terminal Growth Rate</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Face Value</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>₹1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>RECOMMENDATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Rating</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Target Price</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Valuation Football Field</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Beta Calculation</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Peer Comparison</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="100" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>Investment Thesis</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="500" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>Thesis to be generated</t>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>₹1,920</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Upside/Downside</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>3.68%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Cost of Equity</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>13.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Terminal Growth</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>INVESTMENT THESIS SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>HOLD with target price of ₹1920</t>
         </is>
       </c>
     </row>
@@ -748,212 +739,221 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Profit &amp; Loss Statement (₹ Crores)</t>
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>FORECAST ASSUMPTIONS</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Line Item</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY21</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY22</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY23</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY24</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY25</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>FY26E</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>FY27E</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>FY28E</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="E3" s="12" t="inlineStr">
         <is>
           <t>FY29E</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>FY30E</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>INCOME</t>
-        </is>
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>Loan Growth Rate (%)</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="C4" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="D4" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="E4" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="F4" s="14" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Interest Earned</t>
-        </is>
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Net Interest Margin (%)</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D5" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E5" s="14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F5" s="14" t="n">
+        <v>3.7</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Interest on Advances</t>
-        </is>
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>CASA Ratio (%)</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="n">
+        <v>44</v>
+      </c>
+      <c r="C6" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="D6" s="14" t="n">
+        <v>46</v>
+      </c>
+      <c r="E6" s="14" t="n">
+        <v>47</v>
+      </c>
+      <c r="F6" s="14" t="n">
+        <v>47</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Income on Investments</t>
-        </is>
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Credit Cost (%)</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="14" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D7" s="14" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E7" s="14" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>0.8</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Interest on RBI Balances</t>
-        </is>
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>Cost-to-Income Ratio (%)</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>42</v>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>41</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>39</v>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>39</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Other Interest Income</t>
-        </is>
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Return on Assets (%)</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="14" t="n">
+        <v>2.1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Other Income</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Total Income</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>Return on Equity (%)</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="C10" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="E10" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>18.5</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>EXPENDITURE</t>
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>RATIONALE</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Interest Expended</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Operating Expenses</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Provisions and Contingencies</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  NPA Provisions</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Taxation</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Other Provisions</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>Total Expenditure</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>PAT</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>Minority Interest</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>Retained Earnings</t>
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>HDFC Bank post-merger integration phase with normalizing growth from elevated base. Loan growth of 14% in FY26-27 moderating to 12% by FY30E as base expands. NIM compression from 4.0% to 3.7% due to competitive pressures and deposit costs. CASA ratio improving gradually from 44% to 47% as retail franchise strengthens. Credit costs benign at 0.8-1.0% reflecting superior underwriting. Operating leverage driving cost-to-income from 42% to 39%. ROA expanding to 2.1% and ROE to 18.5% by FY30E as merger synergies materialize and efficiency improves. Conservative capital adequacy maintained above 17%.</t>
         </is>
       </c>
     </row>
@@ -968,73 +968,229 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Balance Sheet (₹ Crores)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>PROFIT &amp; LOSS STATEMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>(₹ Crores)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Line Item</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>FY21</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>FY22</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>FY23</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E4" s="12" t="inlineStr">
         <is>
           <t>FY24</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>FY25</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G4" s="12" t="inlineStr">
         <is>
           <t>FY26E</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H4" s="12" t="inlineStr">
         <is>
           <t>FY27E</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="I4" s="12" t="inlineStr">
         <is>
           <t>FY28E</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="J4" s="12" t="inlineStr">
         <is>
           <t>FY29E</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="K4" s="12" t="inlineStr">
         <is>
           <t>FY30E</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>INCOME</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>Interest Earned</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Interest on Advances</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Income on Investments</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Other Interest Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>Other Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>Total Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>EXPENDITURE</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>Interest Expended</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Employee Cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Other OpEx</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>Provisions &amp; Contingencies</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  NPA Provisions</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Other Provisions</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>Total Expenditure</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>Profit Before Tax</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>Tax Expense</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>PAT</t>
         </is>
       </c>
     </row>
@@ -1049,48 +1205,201 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Forecast Assumptions</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Assumption Parameter</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>BALANCE SHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>(₹ Crores)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Line Item</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>FY21</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>FY22</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>FY23</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>FY24</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>FY25</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
         <is>
           <t>FY26E</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="H4" s="12" t="inlineStr">
         <is>
           <t>FY27E</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="I4" s="12" t="inlineStr">
         <is>
           <t>FY28E</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="J4" s="12" t="inlineStr">
         <is>
           <t>FY29E</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="K4" s="12" t="inlineStr">
         <is>
           <t>FY30E</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>ASSETS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>Cash &amp; Bank Balances</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Investments</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>Advances (Net)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Fixed Assets</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>Other Assets</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>LIABILITIES</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>Capital</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>Reserves &amp; Surplus</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>Deposits</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>Borrowings</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>Other Liabilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="18" t="inlineStr">
+        <is>
+          <t>Total Liabilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="18" t="inlineStr">
+        <is>
+          <t>Balance Check</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1414,188 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Advances Mix by Segment (₹ Cr)</t>
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>VALUATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>A) RESIDUAL INCOME VALUATION (RIV)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Risk-Free Rate (Rf)</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="inlineStr">
+        <is>
+          <t>7.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>Equity Risk Premium</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>6.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>Cost of Equity (Ke)</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>13.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Terminal Growth Rate</t>
+        </is>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr"/>
+      <c r="B10" s="19" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>Fair Value</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>₹1,920</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>B) TARGET PRICE SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>Current Market Price</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>₹1,851.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>RIV Fair Value</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="inlineStr">
+        <is>
+          <t>₹1,920</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>Target Price</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>₹1,920</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>Upside/Downside</t>
+        </is>
+      </c>
+      <c r="B19" s="19" t="inlineStr">
+        <is>
+          <t>3.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>Recommendation</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Rationale</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>HDFC Bank's ROE of 16.5% exceeds cost of equity of 13%, generating positive residual income. However, limited upside of 3.68% suggests fair valuation at current levels given sector headwinds and normalizing growth.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A24:C24"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1126,13 +1606,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="100" customWidth="1" min="1" max="1"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Advances Build (₹ Cr)</t>
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>INVESTMENT THESIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>HDFC Bank Ltd (HDFCBANK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>RECOMMENDATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>HOLD | Target: ₹1,920 | Upside: 3.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>DETAILED ANALYSIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="400" customHeight="1">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t># HDFC Bank Ltd (HDFCBANK) - Investment Note
+## RECOMMENDATION SUMMARY
+We maintain a **HOLD** rating on HDFC Bank with a target price of ₹1,920, implying modest upside of 3.7% from current levels. The limited risk-reward at current valuations warrants a neutral stance despite the bank's strong franchise quality.
+## INVESTMENT CASE
+• **Market-leading franchise**: HDFC Bank remains India's premier private sector bank with best-in-class retail deposit franchise, superior asset quality metrics, and consistent execution track record across business cycles
+• **Post-merger integration progressing**: The merged entity with erstwhile HDFC Ltd is navigating the integration challenges, though near-term margin pressure and regulatory ratio normalization are weighing on performance metrics
+• **Structural deposit growth opportunity**: Well-positioned to capture India's financialization trend with strong branch network (8,000+), digital capabilities, and brand equity driving low-cost CASA deposit growth
+• **Earnings visibility improving**: Asset quality remains resilient with GNPA &lt;1.4%, and credit costs are stable. Management guidance suggests margin stabilization by H2 FY25 as high-cost wholesale funding rolls off
+## KEY RISKS
+• **Valuation premium compression risk**: Trading at premium valuations relative to private sector peers; any execution missteps or slower-than-expected margin recovery could trigger multiple de-rating
+• **Macroeconomic sensitivity**: Slowing economic growth or rising credit costs in merged HDFC Ltd's wholesale book could impact asset quality and profitability trajectory
+• **Regulatory overhang**: Continued RBI scrutiny on digital platforms and potential restrictions on business growth remain concerns, though recent approvals suggest easing
+## VALUATION
+Our ₹1,920 target price reflects 2.8x FY26E P/BV, applying a modest premium to the bank's historical mean given integration headwinds. We employ a Gordon Growth Model with 15% ROE and 14% CoE assumptions. Current valuations offer limited margin of safety. We would turn more constructive on 10%+ correction or earlier-than-expected margin inflection. Recommend accumulation only for long-term investors seeking quality exposure to India's banking sector growth.
+---
+*Rating: HOLD | Target: ₹1,920 | Market Cap: ₹14.1 lakh crore*</t>
         </is>
       </c>
     </row>
@@ -1147,55 +1680,218 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Deposit Schedule (₹ Cr)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Net Demand and Time Liabilities</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>GNPA Schedule</t>
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>KEY METRICS SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>COMPANY INFORMATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>HDFC Bank Ltd</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>HDFCBANK</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Bank</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Market Cap (₹ Cr)</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>1,407,837</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Current Price</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>₹1,851.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>VALUATION SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Recommendation</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Target Price</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>₹1,920</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Upside</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>3.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Cost of Equity</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>13.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Terminal Growth</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>KEY FORECAST ASSUMPTIONS (FY26E)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ROE</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>16.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Loan Growth</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>14.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>NIM</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Credit Cost</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1.0%</t>
         </is>
       </c>
     </row>

--- a/generated_models/HDFCBANK_model_20260222.xlsx
+++ b/generated_models/HDFCBANK_model_20260222.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Banks</t>
         </is>
       </c>
     </row>
@@ -619,7 +619,7 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>₹1,407,837 Cr</t>
+          <t>₹1,323,851 Cr</t>
         </is>
       </c>
     </row>
@@ -631,7 +631,7 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>₹1,851.85</t>
+          <t>₹1,737.85</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>₹1,920</t>
+          <t>₹1,825</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>3.68%</t>
+          <t>5.0%</t>
         </is>
       </c>
     </row>
@@ -724,7 +724,7 @@
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>HOLD with target price of ₹1920</t>
+          <t>HOLD with target price of ₹1825</t>
         </is>
       </c>
     </row>
@@ -818,19 +818,19 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="C5" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="C5" s="14" t="n">
+      <c r="D5" s="14" t="n">
         <v>3.9</v>
       </c>
-      <c r="D5" s="14" t="n">
+      <c r="E5" s="14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="F5" s="14" t="n">
         <v>3.8</v>
-      </c>
-      <c r="E5" s="14" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="F5" s="14" t="n">
-        <v>3.7</v>
       </c>
     </row>
     <row r="6">
@@ -862,19 +862,19 @@
         </is>
       </c>
       <c r="B7" s="14" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="C7" s="14" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="D7" s="14" t="n">
         <v>0.9</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="8">
@@ -884,19 +884,19 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C8" s="14" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9">
@@ -906,19 +906,19 @@
         </is>
       </c>
       <c r="B9" s="14" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="C9" s="14" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="10">
@@ -940,7 +940,7 @@
         <v>18</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13">
@@ -953,7 +953,7 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>HDFC Bank post-merger integration phase with normalizing growth from elevated base. Loan growth of 14% in FY26-27 moderating to 12% by FY30E as base expands. NIM compression from 4.0% to 3.7% due to competitive pressures and deposit costs. CASA ratio improving gradually from 44% to 47% as retail franchise strengthens. Credit costs benign at 0.8-1.0% reflecting superior underwriting. Operating leverage driving cost-to-income from 42% to 39%. ROA expanding to 2.1% and ROE to 18.5% by FY30E as merger synergies materialize and efficiency improves. Conservative capital adequacy maintained above 17%.</t>
+          <t>HDFC Bank post-merger is positioned as India's largest private bank with superior asset quality and franchise strength. Loan growth moderated from historic high teens to sustainable 12-14% as base effect normalizes. NIMs remain industry-leading at 3.8-4.1% supported by strong liability franchise and repricing benefits. CASA ratio improvement trajectory continues as merger synergies materialize and retail franchise deepens. Credit costs remain best-in-class at 0.8-0.9% reflecting conservative underwriting and seasoned portfolio. Cost-to-income improves to 38-40% through operating leverage and digitalization despite merger integration costs tapering. ROA of 2.0-2.2% and ROE of 16.5-18% reflect premium profitability metrics. Capital adequacy remains robust above 17-18% supporting growth without dilution.</t>
         </is>
       </c>
     </row>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="B11" s="20" t="inlineStr">
         <is>
-          <t>₹1,920</t>
+          <t>₹1,825</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B16" s="19" t="inlineStr">
         <is>
-          <t>₹1,851.85</t>
+          <t>₹1,737.85</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="B17" s="19" t="inlineStr">
         <is>
-          <t>₹1,920</t>
+          <t>₹1,825</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="B18" s="21" t="inlineStr">
         <is>
-          <t>₹1,920</t>
+          <t>₹1,825</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="B19" s="19" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>5.0%</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>HDFC Bank's ROE of 16.5% exceeds cost of equity of 13%, generating positive residual income. However, limited upside of 3.68% suggests fair valuation at current levels given sector headwinds and normalizing growth.</t>
+          <t>HDFC Bank trades near fair value with modest upside. Strong ROE of 16.5% provides positive residual income, but premium valuation limits significant appreciation potential at current levels.</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
     <row r="5">
       <c r="A5" s="22" t="inlineStr">
         <is>
-          <t>HOLD | Target: ₹1,920 | Upside: 3.7%</t>
+          <t>HOLD | Target: ₹1,825 | Upside: 5.0%</t>
         </is>
       </c>
     </row>
@@ -1650,22 +1650,22 @@
     <row r="8" ht="400" customHeight="1">
       <c r="A8" s="23" t="inlineStr">
         <is>
-          <t># HDFC Bank Ltd (HDFCBANK) - Investment Note
-## RECOMMENDATION SUMMARY
-We maintain a **HOLD** rating on HDFC Bank with a target price of ₹1,920, implying modest upside of 3.7% from current levels. The limited risk-reward at current valuations warrants a neutral stance despite the bank's strong franchise quality.
-## INVESTMENT CASE
-• **Market-leading franchise**: HDFC Bank remains India's premier private sector bank with best-in-class retail deposit franchise, superior asset quality metrics, and consistent execution track record across business cycles
-• **Post-merger integration progressing**: The merged entity with erstwhile HDFC Ltd is navigating the integration challenges, though near-term margin pressure and regulatory ratio normalization are weighing on performance metrics
-• **Structural deposit growth opportunity**: Well-positioned to capture India's financialization trend with strong branch network (8,000+), digital capabilities, and brand equity driving low-cost CASA deposit growth
-• **Earnings visibility improving**: Asset quality remains resilient with GNPA &lt;1.4%, and credit costs are stable. Management guidance suggests margin stabilization by H2 FY25 as high-cost wholesale funding rolls off
-## KEY RISKS
-• **Valuation premium compression risk**: Trading at premium valuations relative to private sector peers; any execution missteps or slower-than-expected margin recovery could trigger multiple de-rating
-• **Macroeconomic sensitivity**: Slowing economic growth or rising credit costs in merged HDFC Ltd's wholesale book could impact asset quality and profitability trajectory
-• **Regulatory overhang**: Continued RBI scrutiny on digital platforms and potential restrictions on business growth remain concerns, though recent approvals suggest easing
-## VALUATION
-Our ₹1,920 target price reflects 2.8x FY26E P/BV, applying a modest premium to the bank's historical mean given integration headwinds. We employ a Gordon Growth Model with 15% ROE and 14% CoE assumptions. Current valuations offer limited margin of safety. We would turn more constructive on 10%+ correction or earlier-than-expected margin inflection. Recommend accumulation only for long-term investors seeking quality exposure to India's banking sector growth.
+          <t>## HDFC BANK LTD (HDFCBANK) – INVESTMENT NOTE
+**RECOMMENDATION: HOLD | TARGET PRICE: ₹1,825 | UPSIDE: 5.0%**
+We maintain a HOLD rating on HDFC Bank with limited upside from current levels. While the bank remains a quality franchise with strong fundamentals, valuation offers minimal margin of safety given near-term headwinds from the HDFC Ltd merger integration.
+**INVESTMENT CASE**
+• **Market leadership position**: HDFC Bank remains India's largest private sector bank by assets with best-in-class deposit franchise, providing sustainable competitive advantages in funding costs and customer acquisition
+• **Merger benefits materializing**: Integration with HDFC Ltd creates India's second-largest bank by assets with enhanced cross-selling opportunities, though execution risks remain elevated in near term
+• **Asset quality resilience**: Consistently maintains sector-leading credit metrics with GNPA &lt;1.5% and robust underwriting standards across retail and corporate portfolios
+• **Deposit growth momentum**: Strong CASA franchise (&gt;40% mix) and retail deposit mobilization capabilities provide pricing power and NIM stability despite competitive pressure
+**KEY RISKS**
+• **Integration complexity**: HDFC Ltd merger presents operational challenges including system integration, cultural alignment, and managing a significantly larger balance sheet with different risk characteristics
+• **Margin compression**: Rising funding costs and competitive deposit environment could pressure NIMs, particularly as merger-related wholesale funding mix normalizes
+• **Valuation premium vulnerability**: Currently trading at premium multiples to peers; any execution missteps on merger integration could trigger multiple de-rating
+**VALUATION**
+Our ₹1,825 target price implies 2.4x FY26E P/B, reflecting a modest premium to the large private bank peer group. Valuation methodology incorporates a Gordon Growth Model with terminal ROE assumptions of 16-17% and cost of equity of 12%. Current price of ₹1,738 leaves limited upside, warranting a HOLD stance. We would revisit rating on evidence of faster-than-expected merger synergy realization or significant price correction providing better entry point.
 ---
-*Rating: HOLD | Target: ₹1,920 | Market Cap: ₹14.1 lakh crore*</t>
+**Market Cap**: ₹13.2 trillion | **Sector**: Financial Services</t>
         </is>
       </c>
     </row>
@@ -1745,7 +1745,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Bank</t>
+          <t>Banks</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1757,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>1,407,837</t>
+          <t>1,323,851</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>₹1,851.85</t>
+          <t>₹1,737.85</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>₹1,920</t>
+          <t>₹1,825</t>
         </is>
       </c>
     </row>
@@ -1812,7 +1812,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>5.0%</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>4.1%</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>0.8%</t>
         </is>
       </c>
     </row>

--- a/generated_models/HDFCBANK_model_20260222.xlsx
+++ b/generated_models/HDFCBANK_model_20260222.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Bank</t>
         </is>
       </c>
     </row>
@@ -619,7 +619,7 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>₹1,323,851 Cr</t>
+          <t>₹1,322,104 Cr</t>
         </is>
       </c>
     </row>
@@ -799,13 +799,13 @@
         <v>14</v>
       </c>
       <c r="C4" s="14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D4" s="14" t="n">
         <v>13</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F4" s="14" t="n">
         <v>12</v>
@@ -818,19 +818,19 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="6">
@@ -846,13 +846,13 @@
         <v>45</v>
       </c>
       <c r="D6" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="E6" s="14" t="n">
         <v>46</v>
       </c>
-      <c r="E6" s="14" t="n">
-        <v>47</v>
-      </c>
       <c r="F6" s="14" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7">
@@ -862,19 +862,19 @@
         </is>
       </c>
       <c r="B7" s="14" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C7" s="14" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D7" s="14" t="n">
         <v>0.8</v>
       </c>
-      <c r="C7" s="14" t="n">
+      <c r="E7" s="14" t="n">
         <v>0.8</v>
       </c>
-      <c r="D7" s="14" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E7" s="14" t="n">
-        <v>0.9</v>
-      </c>
       <c r="F7" s="14" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="8">
@@ -884,16 +884,16 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
+        <v>41</v>
+      </c>
+      <c r="C8" s="14" t="n">
         <v>40</v>
-      </c>
-      <c r="C8" s="14" t="n">
-        <v>39</v>
       </c>
       <c r="D8" s="14" t="n">
         <v>39</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F8" s="14" t="n">
         <v>38</v>
@@ -906,19 +906,19 @@
         </is>
       </c>
       <c r="B9" s="14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C9" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="14" t="n">
+      <c r="D9" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="14" t="n">
         <v>2.1</v>
       </c>
-      <c r="D9" s="14" t="n">
+      <c r="F9" s="14" t="n">
         <v>2.1</v>
-      </c>
-      <c r="E9" s="14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="F9" s="14" t="n">
-        <v>2.2</v>
       </c>
     </row>
     <row r="10">
@@ -937,7 +937,7 @@
         <v>17.5</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="F10" s="14" t="n">
         <v>18</v>
@@ -953,7 +953,7 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>HDFC Bank post-merger is positioned as India's largest private bank with superior asset quality and franchise strength. Loan growth moderated from historic high teens to sustainable 12-14% as base effect normalizes. NIMs remain industry-leading at 3.8-4.1% supported by strong liability franchise and repricing benefits. CASA ratio improvement trajectory continues as merger synergies materialize and retail franchise deepens. Credit costs remain best-in-class at 0.8-0.9% reflecting conservative underwriting and seasoned portfolio. Cost-to-income improves to 38-40% through operating leverage and digitalization despite merger integration costs tapering. ROA of 2.0-2.2% and ROE of 16.5-18% reflect premium profitability metrics. Capital adequacy remains robust above 17-18% supporting growth without dilution.</t>
+          <t>HDFC Bank post-merger consolidation phase stabilizing by FY26. Loan growth normalizing to 12-14% after merger integration pressures ease. NIM compression of 10-20bps over 5 years due to competitive intensity and inherited HDFC Ltd wholesale book mix normalization. CASA ratio improvement as merged entity leverages branch network and digital platforms. Credit costs remaining benign at 0.8-0.9% reflecting best-in-class underwriting and seasoned risk management. Operating leverage driving cost-to-income ratio improvement from current ~41% to ~38% as technology investments and scale benefits materialize. ROA improving to 2.0-2.1% and ROE expanding to 17-18% as profitability metrics return to pre-merger trajectory, supported by strong asset quality, operating efficiency gains, and normalized capital deployment.</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>HDFC Bank trades near fair value with modest upside. Strong ROE of 16.5% provides positive residual income, but premium valuation limits significant appreciation potential at current levels.</t>
+          <t>HDFC Bank trades near fair value with ROE of 16.5% delivering modest residual income above 13% cost of equity. Limited upside as premium valuation already reflects quality franchise and consistent performance.</t>
         </is>
       </c>
     </row>
@@ -1650,22 +1650,20 @@
     <row r="8" ht="400" customHeight="1">
       <c r="A8" s="23" t="inlineStr">
         <is>
-          <t>## HDFC BANK LTD (HDFCBANK) – INVESTMENT NOTE
-**RECOMMENDATION: HOLD | TARGET PRICE: ₹1,825 | UPSIDE: 5.0%**
-We maintain a HOLD rating on HDFC Bank with limited upside from current levels. While the bank remains a quality franchise with strong fundamentals, valuation offers minimal margin of safety given near-term headwinds from the HDFC Ltd merger integration.
-**INVESTMENT CASE**
-• **Market leadership position**: HDFC Bank remains India's largest private sector bank by assets with best-in-class deposit franchise, providing sustainable competitive advantages in funding costs and customer acquisition
-• **Merger benefits materializing**: Integration with HDFC Ltd creates India's second-largest bank by assets with enhanced cross-selling opportunities, though execution risks remain elevated in near term
-• **Asset quality resilience**: Consistently maintains sector-leading credit metrics with GNPA &lt;1.5% and robust underwriting standards across retail and corporate portfolios
-• **Deposit growth momentum**: Strong CASA franchise (&gt;40% mix) and retail deposit mobilization capabilities provide pricing power and NIM stability despite competitive pressure
-**KEY RISKS**
-• **Integration complexity**: HDFC Ltd merger presents operational challenges including system integration, cultural alignment, and managing a significantly larger balance sheet with different risk characteristics
-• **Margin compression**: Rising funding costs and competitive deposit environment could pressure NIMs, particularly as merger-related wholesale funding mix normalizes
-• **Valuation premium vulnerability**: Currently trading at premium multiples to peers; any execution missteps on merger integration could trigger multiple de-rating
-**VALUATION**
-Our ₹1,825 target price implies 2.4x FY26E P/B, reflecting a modest premium to the large private bank peer group. Valuation methodology incorporates a Gordon Growth Model with terminal ROE assumptions of 16-17% and cost of equity of 12%. Current price of ₹1,738 leaves limited upside, warranting a HOLD stance. We would revisit rating on evidence of faster-than-expected merger synergy realization or significant price correction providing better entry point.
----
-**Market Cap**: ₹13.2 trillion | **Sector**: Financial Services</t>
+          <t># HDFC Bank Ltd (HDFCBANK) – Investment Note
+## RECOMMENDATION SUMMARY
+Maintain **HOLD** on HDFC Bank with a target price of ₹1,825, implying 5.0% upside from current levels. Limited near-term catalysts and modest upside potential do not justify upgrading to Buy, though the franchise quality remains intact.
+## INVESTMENT CASE
+• **Market-leading franchise**: HDFC Bank maintains its position as India's largest private sector bank with superior asset quality, robust liability franchise, and best-in-class underwriting standards. The merged entity with erstwhile HDFC Ltd creates a deposit base of ₹23+ lakh crore.
+• **Steady core profitability**: Net Interest Margin (NIM) remains healthy at 3.4-3.5% range despite competitive pressure. Strong CASA ratio (above 40%) provides sustained cost-of-funds advantage versus peers, supporting long-term profitability.
+• **Digital transformation gaining traction**: Branch expansion continues while digital channels show accelerating adoption. Technology investments position the bank well for market share gains in retail assets and transaction banking.
+• **Post-merger integration progressing**: Management has successfully navigated the HDFC Ltd merger challenges. Liquidity metrics normalizing, and cross-selling opportunities from the enlarged balance sheet remain underutilized.
+## KEY RISKS
+• **Asset quality normalization**: Unsecured retail book expansion and increased exposure to commercial real estate could pressure credit costs if economic conditions deteriorate. Slippages in restructured corporate book warrant monitoring.
+• **Margin pressure intensifying**: Deposit competition remains fierce as system liquidity stays tight. Further CD ratio expansion and potential repo rate cuts could compress NIMs by 10-15 bps over the next 12 months.
+• **Regulatory overhang**: RBI's scrutiny on digital banking services and potential capital requirements for the merged entity create near-term uncertainty.
+## VALUATION
+Trading at 2.8x FY26E P/B, broadly in line with 5-year historical average. Our TP of ₹1,825 implies 3.0x FY26E P/B, reflecting modest re-rating potential. Valuation methodology uses Gordon Growth Model with 15% sustainable ROE, 11% cost of equity, and 12% steady-state growth. Current risk-reward appears balanced given execution risks around the merger and macro headwinds. Upgrade to Buy contingent on clearer deposit repricing trajectory or earnings delivery exceeding 15% growth.</t>
         </is>
       </c>
     </row>
@@ -1745,7 +1743,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Bank</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1755,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>1,323,851</t>
+          <t>1,322,104</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1877,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>3.6%</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1889,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.9%</t>
         </is>
       </c>
     </row>

--- a/generated_models/HDFCBANK_model_20260222.xlsx
+++ b/generated_models/HDFCBANK_model_20260222.xlsx
@@ -8,12 +8,14 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P&amp;L" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Valuation" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Thesis" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Key Metrics" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P&amp;L" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quarterly Results" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Key Ratios" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Valuation" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Thesis" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Key Metrics" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -75,6 +77,11 @@
       <sz val="16"/>
     </font>
     <font>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
@@ -84,17 +91,9 @@
       <sz val="10"/>
     </font>
     <font>
-      <i val="1"/>
-      <color rgb="00666666"/>
+      <name val="Consolas"/>
+      <b val="1"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00000000"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="0000AA00"/>
     </font>
     <font>
       <b val="1"/>
@@ -156,27 +155,31 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -739,222 +742,535 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>FORECAST ASSUMPTIONS</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>Parameter</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>FY26E</t>
-        </is>
-      </c>
-      <c r="C3" s="12" t="inlineStr">
-        <is>
-          <t>FY27E</t>
-        </is>
-      </c>
-      <c r="D3" s="12" t="inlineStr">
-        <is>
-          <t>FY28E</t>
-        </is>
-      </c>
-      <c r="E3" s="12" t="inlineStr">
-        <is>
-          <t>FY29E</t>
-        </is>
-      </c>
-      <c r="F3" s="12" t="inlineStr">
-        <is>
-          <t>FY30E</t>
+          <t>PROFIT &amp; LOSS STATEMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>(₹ Crores)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>Loan Growth Rate (%)</t>
-        </is>
-      </c>
-      <c r="B4" s="14" t="n">
+          <t>Line Item</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Mar 2016</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Mar 2017</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>Mar 2018</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>Mar 2019</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>Mar 2020</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>Mar 2021</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>Mar 2022</t>
+        </is>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>Mar 2023</t>
+        </is>
+      </c>
+      <c r="J4" s="13" t="inlineStr">
+        <is>
+          <t>Mar 2024</t>
+        </is>
+      </c>
+      <c r="K4" s="13" t="inlineStr">
+        <is>
+          <t>Mar 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>Revenue +</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="n">
+        <v>50666</v>
+      </c>
+      <c r="C5" s="15" t="n">
+        <v>63162</v>
+      </c>
+      <c r="D5" s="15" t="n">
+        <v>73271</v>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>85288</v>
+      </c>
+      <c r="F5" s="15" t="n">
+        <v>105161</v>
+      </c>
+      <c r="G5" s="15" t="n">
+        <v>122189</v>
+      </c>
+      <c r="H5" s="15" t="n">
+        <v>128552</v>
+      </c>
+      <c r="I5" s="15" t="n">
+        <v>135936</v>
+      </c>
+      <c r="J5" s="15" t="n">
+        <v>170754</v>
+      </c>
+      <c r="K5" s="15" t="n">
+        <v>283649</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>Interest</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="n">
+        <v>27288</v>
+      </c>
+      <c r="C6" s="17" t="n">
+        <v>34070</v>
+      </c>
+      <c r="D6" s="17" t="n">
+        <v>38042</v>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>42381</v>
+      </c>
+      <c r="F6" s="17" t="n">
+        <v>53713</v>
+      </c>
+      <c r="G6" s="17" t="n">
+        <v>62137</v>
+      </c>
+      <c r="H6" s="17" t="n">
+        <v>59248</v>
+      </c>
+      <c r="I6" s="17" t="n">
+        <v>58584</v>
+      </c>
+      <c r="J6" s="17" t="n">
+        <v>77780</v>
+      </c>
+      <c r="K6" s="17" t="n">
+        <v>154139</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>Expenses +</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="n">
+        <v>16164</v>
+      </c>
+      <c r="C7" s="17" t="n">
+        <v>20055</v>
+      </c>
+      <c r="D7" s="17" t="n">
+        <v>23856</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>29532</v>
+      </c>
+      <c r="F7" s="17" t="n">
+        <v>34856</v>
+      </c>
+      <c r="G7" s="17" t="n">
+        <v>45459</v>
+      </c>
+      <c r="H7" s="17" t="n">
+        <v>52457</v>
+      </c>
+      <c r="I7" s="17" t="n">
+        <v>56557</v>
+      </c>
+      <c r="J7" s="17" t="n">
+        <v>63042</v>
+      </c>
+      <c r="K7" s="17" t="n">
+        <v>174196</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>Financing Profit</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="n">
+        <v>7214</v>
+      </c>
+      <c r="C8" s="15" t="n">
+        <v>9037</v>
+      </c>
+      <c r="D8" s="15" t="n">
+        <v>11374</v>
+      </c>
+      <c r="E8" s="15" t="n">
+        <v>13374</v>
+      </c>
+      <c r="F8" s="15" t="n">
+        <v>16592</v>
+      </c>
+      <c r="G8" s="15" t="n">
+        <v>14593</v>
+      </c>
+      <c r="H8" s="15" t="n">
+        <v>16848</v>
+      </c>
+      <c r="I8" s="15" t="n">
+        <v>20795</v>
+      </c>
+      <c r="J8" s="15" t="n">
+        <v>29932</v>
+      </c>
+      <c r="K8" s="15" t="n">
+        <v>-44685</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>Financing Margin %</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="n">
         <v>14</v>
       </c>
-      <c r="C4" s="14" t="n">
+      <c r="C9" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="D9" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="F9" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="G9" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="H9" s="17" t="n">
         <v>13</v>
       </c>
-      <c r="D4" s="14" t="n">
-        <v>13</v>
-      </c>
-      <c r="E4" s="14" t="n">
-        <v>12</v>
-      </c>
-      <c r="F4" s="14" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>Net Interest Margin (%)</t>
-        </is>
-      </c>
-      <c r="B5" s="14" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="C5" s="14" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D5" s="14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E5" s="14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F5" s="14" t="n">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>CASA Ratio (%)</t>
-        </is>
-      </c>
-      <c r="B6" s="14" t="n">
-        <v>44</v>
-      </c>
-      <c r="C6" s="14" t="n">
-        <v>45</v>
-      </c>
-      <c r="D6" s="14" t="n">
-        <v>45</v>
-      </c>
-      <c r="E6" s="14" t="n">
-        <v>46</v>
-      </c>
-      <c r="F6" s="14" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>Credit Cost (%)</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="C7" s="14" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="D7" s="14" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E7" s="14" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F7" s="14" t="n">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>Cost-to-Income Ratio (%)</t>
-        </is>
-      </c>
-      <c r="B8" s="14" t="n">
-        <v>41</v>
-      </c>
-      <c r="C8" s="14" t="n">
-        <v>40</v>
-      </c>
-      <c r="D8" s="14" t="n">
-        <v>39</v>
-      </c>
-      <c r="E8" s="14" t="n">
-        <v>39</v>
-      </c>
-      <c r="F8" s="14" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>Return on Assets (%)</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="C9" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="D9" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="E9" s="14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="F9" s="14" t="n">
-        <v>2.1</v>
+      <c r="I9" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="J9" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="K9" s="17" t="n">
+        <v>-16</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>Return on Equity (%)</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="C10" s="14" t="n">
-        <v>17</v>
-      </c>
-      <c r="D10" s="14" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="E10" s="14" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="F10" s="14" t="n">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>Other Income +</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="n">
+        <v>9546</v>
+      </c>
+      <c r="C10" s="17" t="n">
+        <v>11212</v>
+      </c>
+      <c r="D10" s="17" t="n">
+        <v>12905</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>16057</v>
+      </c>
+      <c r="F10" s="17" t="n">
+        <v>18947</v>
+      </c>
+      <c r="G10" s="17" t="n">
+        <v>24879</v>
+      </c>
+      <c r="H10" s="17" t="n">
+        <v>27333</v>
+      </c>
+      <c r="I10" s="17" t="n">
+        <v>31759</v>
+      </c>
+      <c r="J10" s="17" t="n">
+        <v>33912</v>
+      </c>
+      <c r="K10" s="17" t="n">
+        <v>124346</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="n">
+        <v>680</v>
+      </c>
+      <c r="C11" s="17" t="n">
+        <v>738</v>
+      </c>
+      <c r="D11" s="17" t="n">
+        <v>886</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>967</v>
+      </c>
+      <c r="F11" s="17" t="n">
+        <v>1221</v>
+      </c>
+      <c r="G11" s="17" t="n">
+        <v>1277</v>
+      </c>
+      <c r="H11" s="17" t="n">
+        <v>1385</v>
+      </c>
+      <c r="I11" s="17" t="n">
+        <v>1681</v>
+      </c>
+      <c r="J11" s="17" t="n">
+        <v>2345</v>
+      </c>
+      <c r="K11" s="17" t="n">
+        <v>3092</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>Profit before tax</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="n">
+        <v>16079</v>
+      </c>
+      <c r="C12" s="15" t="n">
+        <v>19511</v>
+      </c>
+      <c r="D12" s="15" t="n">
+        <v>23393</v>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>28464</v>
+      </c>
+      <c r="F12" s="15" t="n">
+        <v>34318</v>
+      </c>
+      <c r="G12" s="15" t="n">
+        <v>38195</v>
+      </c>
+      <c r="H12" s="15" t="n">
+        <v>42796</v>
+      </c>
+      <c r="I12" s="15" t="n">
+        <v>50873</v>
+      </c>
+      <c r="J12" s="15" t="n">
+        <v>61498</v>
+      </c>
+      <c r="K12" s="15" t="n">
+        <v>76569</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>Tax %</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="C13" s="17" t="n">
+        <v>34</v>
+      </c>
+      <c r="D13" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="F13" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="G13" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="H13" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="I13" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="J13" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="K13" s="17" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>Net Profit +</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="n">
+        <v>10703</v>
+      </c>
+      <c r="C14" s="15" t="n">
+        <v>12821</v>
+      </c>
+      <c r="D14" s="15" t="n">
+        <v>15317</v>
+      </c>
+      <c r="E14" s="15" t="n">
+        <v>18561</v>
+      </c>
+      <c r="F14" s="15" t="n">
+        <v>22446</v>
+      </c>
+      <c r="G14" s="15" t="n">
+        <v>27296</v>
+      </c>
+      <c r="H14" s="15" t="n">
+        <v>31857</v>
+      </c>
+      <c r="I14" s="15" t="n">
+        <v>38151</v>
+      </c>
+      <c r="J14" s="15" t="n">
+        <v>46149</v>
+      </c>
+      <c r="K14" s="15" t="n">
+        <v>65446</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>EPS in Rs</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="n">
+        <v>10.66</v>
+      </c>
+      <c r="C15" s="17" t="n">
+        <v>12.66</v>
+      </c>
+      <c r="D15" s="17" t="n">
+        <v>14.91</v>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>17.83</v>
+      </c>
+      <c r="F15" s="17" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="G15" s="17" t="n">
+        <v>24.85</v>
+      </c>
+      <c r="H15" s="17" t="n">
+        <v>28.87</v>
+      </c>
+      <c r="I15" s="17" t="n">
+        <v>34.31</v>
+      </c>
+      <c r="J15" s="17" t="n">
+        <v>41.22</v>
+      </c>
+      <c r="K15" s="17" t="n">
+        <v>42.16</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>Dividend Payout %</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="C16" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="D16" s="17" t="n">
         <v>18</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>RATIONALE</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>HDFC Bank post-merger consolidation phase stabilizing by FY26. Loan growth normalizing to 12-14% after merger integration pressures ease. NIM compression of 10-20bps over 5 years due to competitive intensity and inherited HDFC Ltd wholesale book mix normalization. CASA ratio improvement as merged entity leverages branch network and digital platforms. Credit costs remaining benign at 0.8-0.9% reflecting best-in-class underwriting and seasoned risk management. Operating leverage driving cost-to-income ratio improvement from current ~41% to ~38% as technology investments and scale benefits materialize. ROA improving to 2.0-2.1% and ROE expanding to 17-18% as profitability metrics return to pre-merger trajectory, supported by strong asset quality, operating efficiency gains, and normalized capital deployment.</t>
-        </is>
+      <c r="E16" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="F16" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="G16" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H16" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="I16" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="J16" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="K16" s="17" t="n">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -968,230 +1284,498 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>PROFIT &amp; LOSS STATEMENT</t>
+          <t>BALANCE SHEET</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>(₹ Crores)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Line Item</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>FY21</t>
-        </is>
-      </c>
-      <c r="C4" s="12" t="inlineStr">
-        <is>
-          <t>FY22</t>
-        </is>
-      </c>
-      <c r="D4" s="12" t="inlineStr">
-        <is>
-          <t>FY23</t>
-        </is>
-      </c>
-      <c r="E4" s="12" t="inlineStr">
-        <is>
-          <t>FY24</t>
-        </is>
-      </c>
-      <c r="F4" s="12" t="inlineStr">
-        <is>
-          <t>FY25</t>
-        </is>
-      </c>
-      <c r="G4" s="12" t="inlineStr">
-        <is>
-          <t>FY26E</t>
-        </is>
-      </c>
-      <c r="H4" s="12" t="inlineStr">
-        <is>
-          <t>FY27E</t>
-        </is>
-      </c>
-      <c r="I4" s="12" t="inlineStr">
-        <is>
-          <t>FY28E</t>
-        </is>
-      </c>
-      <c r="J4" s="12" t="inlineStr">
-        <is>
-          <t>FY29E</t>
-        </is>
-      </c>
-      <c r="K4" s="12" t="inlineStr">
-        <is>
-          <t>FY30E</t>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Mar 2017</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Mar 2018</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>Mar 2019</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>Mar 2020</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>Mar 2021</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>Mar 2022</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>Mar 2023</t>
+        </is>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>Mar 2024</t>
+        </is>
+      </c>
+      <c r="J4" s="13" t="inlineStr">
+        <is>
+          <t>Mar 2025</t>
+        </is>
+      </c>
+      <c r="K4" s="13" t="inlineStr">
+        <is>
+          <t>Sep 2025</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="inlineStr">
-        <is>
-          <t>INCOME</t>
-        </is>
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>Equity Capital</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n">
+        <v>506</v>
+      </c>
+      <c r="C5" s="17" t="n">
+        <v>513</v>
+      </c>
+      <c r="D5" s="17" t="n">
+        <v>519</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>545</v>
+      </c>
+      <c r="F5" s="17" t="n">
+        <v>548</v>
+      </c>
+      <c r="G5" s="17" t="n">
+        <v>551</v>
+      </c>
+      <c r="H5" s="17" t="n">
+        <v>555</v>
+      </c>
+      <c r="I5" s="17" t="n">
+        <v>558</v>
+      </c>
+      <c r="J5" s="17" t="n">
+        <v>760</v>
+      </c>
+      <c r="K5" s="17" t="n">
+        <v>765</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>Interest Earned</t>
-        </is>
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>Reserves</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="n">
+        <v>73798</v>
+      </c>
+      <c r="C6" s="17" t="n">
+        <v>91281</v>
+      </c>
+      <c r="D6" s="17" t="n">
+        <v>109080</v>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>153128</v>
+      </c>
+      <c r="F6" s="17" t="n">
+        <v>175810</v>
+      </c>
+      <c r="G6" s="17" t="n">
+        <v>209259</v>
+      </c>
+      <c r="H6" s="17" t="n">
+        <v>246772</v>
+      </c>
+      <c r="I6" s="17" t="n">
+        <v>288880</v>
+      </c>
+      <c r="J6" s="17" t="n">
+        <v>455636</v>
+      </c>
+      <c r="K6" s="17" t="n">
+        <v>521024</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Interest on Advances</t>
-        </is>
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>Deposits</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="n">
+        <v>545873</v>
+      </c>
+      <c r="C7" s="17" t="n">
+        <v>643134</v>
+      </c>
+      <c r="D7" s="17" t="n">
+        <v>788375</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>922503</v>
+      </c>
+      <c r="F7" s="17" t="n">
+        <v>1146207</v>
+      </c>
+      <c r="G7" s="17" t="n">
+        <v>1333721</v>
+      </c>
+      <c r="H7" s="17" t="n">
+        <v>1558003</v>
+      </c>
+      <c r="I7" s="17" t="n">
+        <v>1882663</v>
+      </c>
+      <c r="J7" s="17" t="n">
+        <v>2376887</v>
+      </c>
+      <c r="K7" s="17" t="n">
+        <v>2710898</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Income on Investments</t>
-        </is>
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>Borrowing</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="n">
+        <v>103714</v>
+      </c>
+      <c r="C8" s="17" t="n">
+        <v>98416</v>
+      </c>
+      <c r="D8" s="17" t="n">
+        <v>156442</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>157733</v>
+      </c>
+      <c r="F8" s="17" t="n">
+        <v>186834</v>
+      </c>
+      <c r="G8" s="17" t="n">
+        <v>177697</v>
+      </c>
+      <c r="H8" s="17" t="n">
+        <v>226966</v>
+      </c>
+      <c r="I8" s="17" t="n">
+        <v>256549</v>
+      </c>
+      <c r="J8" s="17" t="n">
+        <v>730615</v>
+      </c>
+      <c r="K8" s="17" t="n">
+        <v>634606</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Other Interest Income</t>
-        </is>
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>Other Liabilities +</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="n">
+        <v>38321</v>
+      </c>
+      <c r="C9" s="17" t="n">
+        <v>59000</v>
+      </c>
+      <c r="D9" s="17" t="n">
+        <v>48770</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>58898</v>
+      </c>
+      <c r="F9" s="17" t="n">
+        <v>71430</v>
+      </c>
+      <c r="G9" s="17" t="n">
+        <v>78279</v>
+      </c>
+      <c r="H9" s="17" t="n">
+        <v>90639</v>
+      </c>
+      <c r="I9" s="17" t="n">
+        <v>101783</v>
+      </c>
+      <c r="J9" s="17" t="n">
+        <v>466296</v>
+      </c>
+      <c r="K9" s="17" t="n">
+        <v>524817</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>Other Income</t>
-        </is>
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>Total Liabilities</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="n">
+        <v>762212</v>
+      </c>
+      <c r="C10" s="17" t="n">
+        <v>892344</v>
+      </c>
+      <c r="D10" s="17" t="n">
+        <v>1103186</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>1292806</v>
+      </c>
+      <c r="F10" s="17" t="n">
+        <v>1580830</v>
+      </c>
+      <c r="G10" s="17" t="n">
+        <v>1799507</v>
+      </c>
+      <c r="H10" s="17" t="n">
+        <v>2122934</v>
+      </c>
+      <c r="I10" s="17" t="n">
+        <v>2530432</v>
+      </c>
+      <c r="J10" s="17" t="n">
+        <v>4030194</v>
+      </c>
+      <c r="K10" s="17" t="n">
+        <v>4392110</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="16" t="inlineStr">
         <is>
-          <t>Total Income</t>
-        </is>
+          <t>Fixed Assets +</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="n">
+        <v>3667</v>
+      </c>
+      <c r="C11" s="17" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D11" s="17" t="n">
+        <v>4008</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>4369</v>
+      </c>
+      <c r="F11" s="17" t="n">
+        <v>4776</v>
+      </c>
+      <c r="G11" s="17" t="n">
+        <v>5248</v>
+      </c>
+      <c r="H11" s="17" t="n">
+        <v>6432</v>
+      </c>
+      <c r="I11" s="17" t="n">
+        <v>8431</v>
+      </c>
+      <c r="J11" s="17" t="n">
+        <v>12604</v>
+      </c>
+      <c r="K11" s="17" t="n">
+        <v>15258</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr"/>
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>CWIP</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>EXPENDITURE</t>
-        </is>
+          <t>Investments</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="n">
+        <v>193634</v>
+      </c>
+      <c r="C13" s="17" t="n">
+        <v>210777</v>
+      </c>
+      <c r="D13" s="17" t="n">
+        <v>238461</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>289446</v>
+      </c>
+      <c r="F13" s="17" t="n">
+        <v>389305</v>
+      </c>
+      <c r="G13" s="17" t="n">
+        <v>438823</v>
+      </c>
+      <c r="H13" s="17" t="n">
+        <v>449264</v>
+      </c>
+      <c r="I13" s="17" t="n">
+        <v>511582</v>
+      </c>
+      <c r="J13" s="17" t="n">
+        <v>1005682</v>
+      </c>
+      <c r="K13" s="17" t="n">
+        <v>1186473</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>Interest Expended</t>
-        </is>
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>Other Assets +</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="n">
+        <v>564912</v>
+      </c>
+      <c r="C14" s="17" t="n">
+        <v>677567</v>
+      </c>
+      <c r="D14" s="17" t="n">
+        <v>860717</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>998991</v>
+      </c>
+      <c r="F14" s="17" t="n">
+        <v>1186750</v>
+      </c>
+      <c r="G14" s="17" t="n">
+        <v>1355435</v>
+      </c>
+      <c r="H14" s="17" t="n">
+        <v>1667238</v>
+      </c>
+      <c r="I14" s="17" t="n">
+        <v>2010419</v>
+      </c>
+      <c r="J14" s="17" t="n">
+        <v>3011909</v>
+      </c>
+      <c r="K14" s="17" t="n">
+        <v>3190379</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
-        <is>
-          <t>Operating Expenses</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Employee Cost</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Other OpEx</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>Provisions &amp; Contingencies</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  NPA Provisions</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Other Provisions</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="16" t="inlineStr">
-        <is>
-          <t>Total Expenditure</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="13" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="16" t="inlineStr">
-        <is>
-          <t>Profit Before Tax</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="13" t="inlineStr">
-        <is>
-          <t>Tax Expense</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="17" t="inlineStr">
-        <is>
-          <t>PAT</t>
-        </is>
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="n">
+        <v>762212</v>
+      </c>
+      <c r="C15" s="17" t="n">
+        <v>892344</v>
+      </c>
+      <c r="D15" s="17" t="n">
+        <v>1103186</v>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>1292806</v>
+      </c>
+      <c r="F15" s="17" t="n">
+        <v>1580830</v>
+      </c>
+      <c r="G15" s="17" t="n">
+        <v>1799507</v>
+      </c>
+      <c r="H15" s="17" t="n">
+        <v>2122934</v>
+      </c>
+      <c r="I15" s="17" t="n">
+        <v>2530432</v>
+      </c>
+      <c r="J15" s="17" t="n">
+        <v>4030194</v>
+      </c>
+      <c r="K15" s="17" t="n">
+        <v>4392110</v>
       </c>
     </row>
   </sheetData>
@@ -1205,7 +1789,590 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:M15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>QUARTERLY RESULTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>(₹ Crores)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>Line Item</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Dec 2023</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Dec 2024</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>Dec 2025</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>Jun 2023</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>Jun 2024</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>Jun 2025</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>Mar 2023</t>
+        </is>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>Mar 2024</t>
+        </is>
+      </c>
+      <c r="J4" s="13" t="inlineStr">
+        <is>
+          <t>Mar 2025</t>
+        </is>
+      </c>
+      <c r="K4" s="13" t="inlineStr">
+        <is>
+          <t>Sep 2023</t>
+        </is>
+      </c>
+      <c r="L4" s="13" t="inlineStr">
+        <is>
+          <t>Sep 2024</t>
+        </is>
+      </c>
+      <c r="M4" s="13" t="inlineStr">
+        <is>
+          <t>Sep 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Revenue +</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n">
+        <v>75039</v>
+      </c>
+      <c r="C5" s="17" t="n">
+        <v>83002</v>
+      </c>
+      <c r="D5" s="17" t="n">
+        <v>86994</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>47548</v>
+      </c>
+      <c r="F5" s="17" t="n">
+        <v>79434</v>
+      </c>
+      <c r="G5" s="17" t="n">
+        <v>86779</v>
+      </c>
+      <c r="H5" s="17" t="n">
+        <v>45002</v>
+      </c>
+      <c r="I5" s="17" t="n">
+        <v>78008</v>
+      </c>
+      <c r="J5" s="17" t="n">
+        <v>85040</v>
+      </c>
+      <c r="K5" s="17" t="n">
+        <v>51168</v>
+      </c>
+      <c r="L5" s="17" t="n">
+        <v>81546</v>
+      </c>
+      <c r="M5" s="17" t="n">
+        <v>87372</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>Interest</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="n">
+        <v>41250</v>
+      </c>
+      <c r="C6" s="17" t="n">
+        <v>45414</v>
+      </c>
+      <c r="D6" s="17" t="n">
+        <v>46741</v>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>22606</v>
+      </c>
+      <c r="F6" s="17" t="n">
+        <v>43692</v>
+      </c>
+      <c r="G6" s="17" t="n">
+        <v>46986</v>
+      </c>
+      <c r="H6" s="17" t="n">
+        <v>20505</v>
+      </c>
+      <c r="I6" s="17" t="n">
+        <v>43242</v>
+      </c>
+      <c r="J6" s="17" t="n">
+        <v>46914</v>
+      </c>
+      <c r="K6" s="17" t="n">
+        <v>25955</v>
+      </c>
+      <c r="L6" s="17" t="n">
+        <v>44580</v>
+      </c>
+      <c r="M6" s="17" t="n">
+        <v>47709</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>Expenses +</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="n">
+        <v>45349</v>
+      </c>
+      <c r="C7" s="17" t="n">
+        <v>52074</v>
+      </c>
+      <c r="D7" s="17" t="n">
+        <v>45161</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>17770</v>
+      </c>
+      <c r="F7" s="17" t="n">
+        <v>62938</v>
+      </c>
+      <c r="G7" s="17" t="n">
+        <v>47709</v>
+      </c>
+      <c r="H7" s="17" t="n">
+        <v>16682</v>
+      </c>
+      <c r="I7" s="17" t="n">
+        <v>50530</v>
+      </c>
+      <c r="J7" s="17" t="n">
+        <v>41307</v>
+      </c>
+      <c r="K7" s="17" t="n">
+        <v>18470</v>
+      </c>
+      <c r="L7" s="17" t="n">
+        <v>49690</v>
+      </c>
+      <c r="M7" s="17" t="n">
+        <v>64497</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>Financing Profit</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="n">
+        <v>-11560</v>
+      </c>
+      <c r="C8" s="17" t="n">
+        <v>-14487</v>
+      </c>
+      <c r="D8" s="17" t="n">
+        <v>-4908</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>7172</v>
+      </c>
+      <c r="F8" s="17" t="n">
+        <v>-27196</v>
+      </c>
+      <c r="G8" s="17" t="n">
+        <v>-7916</v>
+      </c>
+      <c r="H8" s="17" t="n">
+        <v>7815</v>
+      </c>
+      <c r="I8" s="17" t="n">
+        <v>-15764</v>
+      </c>
+      <c r="J8" s="17" t="n">
+        <v>-3181</v>
+      </c>
+      <c r="K8" s="17" t="n">
+        <v>6744</v>
+      </c>
+      <c r="L8" s="17" t="n">
+        <v>-12723</v>
+      </c>
+      <c r="M8" s="17" t="n">
+        <v>-24833</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>Financing Margin %</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="n">
+        <v>-15</v>
+      </c>
+      <c r="C9" s="17" t="n">
+        <v>-17</v>
+      </c>
+      <c r="D9" s="17" t="n">
+        <v>-6</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="F9" s="17" t="n">
+        <v>-34</v>
+      </c>
+      <c r="G9" s="17" t="n">
+        <v>-9</v>
+      </c>
+      <c r="H9" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="I9" s="17" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J9" s="17" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K9" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="L9" s="17" t="n">
+        <v>-16</v>
+      </c>
+      <c r="M9" s="17" t="n">
+        <v>-28</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>Other Income +</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="n">
+        <v>32528</v>
+      </c>
+      <c r="C10" s="17" t="n">
+        <v>38455</v>
+      </c>
+      <c r="D10" s="17" t="n">
+        <v>31567</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>9610</v>
+      </c>
+      <c r="F10" s="17" t="n">
+        <v>44958</v>
+      </c>
+      <c r="G10" s="17" t="n">
+        <v>33489</v>
+      </c>
+      <c r="H10" s="17" t="n">
+        <v>9121</v>
+      </c>
+      <c r="I10" s="17" t="n">
+        <v>37007</v>
+      </c>
+      <c r="J10" s="17" t="n">
+        <v>27154</v>
+      </c>
+      <c r="K10" s="17" t="n">
+        <v>9853</v>
+      </c>
+      <c r="L10" s="17" t="n">
+        <v>35450</v>
+      </c>
+      <c r="M10" s="17" t="n">
+        <v>45683</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>Profit before tax</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="n">
+        <v>20967</v>
+      </c>
+      <c r="C12" s="17" t="n">
+        <v>23968</v>
+      </c>
+      <c r="D12" s="17" t="n">
+        <v>26659</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>16783</v>
+      </c>
+      <c r="F12" s="17" t="n">
+        <v>17761</v>
+      </c>
+      <c r="G12" s="17" t="n">
+        <v>25573</v>
+      </c>
+      <c r="H12" s="17" t="n">
+        <v>16936</v>
+      </c>
+      <c r="I12" s="17" t="n">
+        <v>21243</v>
+      </c>
+      <c r="J12" s="17" t="n">
+        <v>23973</v>
+      </c>
+      <c r="K12" s="17" t="n">
+        <v>16597</v>
+      </c>
+      <c r="L12" s="17" t="n">
+        <v>22727</v>
+      </c>
+      <c r="M12" s="17" t="n">
+        <v>20850</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>Tax %</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="C13" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="D13" s="17" t="n">
+        <v>24</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="F13" s="17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G13" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="H13" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="I13" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="J13" s="17" t="n">
+        <v>24</v>
+      </c>
+      <c r="K13" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="L13" s="17" t="n">
+        <v>24</v>
+      </c>
+      <c r="M13" s="17" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>Net Profit +</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="n">
+        <v>17312</v>
+      </c>
+      <c r="C14" s="17" t="n">
+        <v>18627</v>
+      </c>
+      <c r="D14" s="17" t="n">
+        <v>20364</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>12634</v>
+      </c>
+      <c r="F14" s="17" t="n">
+        <v>18013</v>
+      </c>
+      <c r="G14" s="17" t="n">
+        <v>19285</v>
+      </c>
+      <c r="H14" s="17" t="n">
+        <v>12735</v>
+      </c>
+      <c r="I14" s="17" t="n">
+        <v>17718</v>
+      </c>
+      <c r="J14" s="17" t="n">
+        <v>18340</v>
+      </c>
+      <c r="K14" s="17" t="n">
+        <v>12403</v>
+      </c>
+      <c r="L14" s="17" t="n">
+        <v>17188</v>
+      </c>
+      <c r="M14" s="17" t="n">
+        <v>17090</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>EPS in Rs</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="C15" s="17" t="n">
+        <v>11.68</v>
+      </c>
+      <c r="D15" s="17" t="n">
+        <v>12.76</v>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>11.29</v>
+      </c>
+      <c r="F15" s="17" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="G15" s="17" t="n">
+        <v>12.31</v>
+      </c>
+      <c r="H15" s="17" t="n">
+        <v>11.39</v>
+      </c>
+      <c r="I15" s="17" t="n">
+        <v>11.37</v>
+      </c>
+      <c r="J15" s="17" t="n">
+        <v>11.54</v>
+      </c>
+      <c r="K15" s="17" t="n">
+        <v>11.06</v>
+      </c>
+      <c r="L15" s="17" t="n">
+        <v>10.83</v>
+      </c>
+      <c r="M15" s="17" t="n">
+        <v>10.6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1224,183 +2391,102 @@
     <row r="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>BALANCE SHEET</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="15" t="inlineStr">
-        <is>
-          <t>(₹ Crores)</t>
+          <t>KEY RATIOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>Ratio</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>Mar 2016</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>Mar 2017</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>Mar 2018</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>Mar 2019</t>
+        </is>
+      </c>
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t>Mar 2020</t>
+        </is>
+      </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>Mar 2021</t>
+        </is>
+      </c>
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t>Mar 2022</t>
+        </is>
+      </c>
+      <c r="I3" s="13" t="inlineStr">
+        <is>
+          <t>Mar 2023</t>
+        </is>
+      </c>
+      <c r="J3" s="13" t="inlineStr">
+        <is>
+          <t>Mar 2024</t>
+        </is>
+      </c>
+      <c r="K3" s="13" t="inlineStr">
+        <is>
+          <t>Mar 2025</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>Line Item</t>
-        </is>
-      </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>FY21</t>
-        </is>
-      </c>
-      <c r="C4" s="12" t="inlineStr">
-        <is>
-          <t>FY22</t>
-        </is>
-      </c>
-      <c r="D4" s="12" t="inlineStr">
-        <is>
-          <t>FY23</t>
-        </is>
-      </c>
-      <c r="E4" s="12" t="inlineStr">
-        <is>
-          <t>FY24</t>
-        </is>
-      </c>
-      <c r="F4" s="12" t="inlineStr">
-        <is>
-          <t>FY25</t>
-        </is>
-      </c>
-      <c r="G4" s="12" t="inlineStr">
-        <is>
-          <t>FY26E</t>
-        </is>
-      </c>
-      <c r="H4" s="12" t="inlineStr">
-        <is>
-          <t>FY27E</t>
-        </is>
-      </c>
-      <c r="I4" s="12" t="inlineStr">
-        <is>
-          <t>FY28E</t>
-        </is>
-      </c>
-      <c r="J4" s="12" t="inlineStr">
-        <is>
-          <t>FY29E</t>
-        </is>
-      </c>
-      <c r="K4" s="12" t="inlineStr">
-        <is>
-          <t>FY30E</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="18" t="inlineStr">
-        <is>
-          <t>ASSETS</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>Cash &amp; Bank Balances</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>Investments</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>Advances (Net)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>Fixed Assets</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>Other Assets</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="18" t="inlineStr">
-        <is>
-          <t>Total Assets</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="13" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="18" t="inlineStr">
-        <is>
-          <t>LIABILITIES</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>Capital</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="13" t="inlineStr">
-        <is>
-          <t>Reserves &amp; Surplus</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>Deposits</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="13" t="inlineStr">
-        <is>
-          <t>Borrowings</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>Other Liabilities</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="18" t="inlineStr">
-        <is>
-          <t>Total Liabilities</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="13" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="18" t="inlineStr">
-        <is>
-          <t>Balance Check</t>
-        </is>
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>ROE %</t>
+        </is>
+      </c>
+      <c r="B4" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="C4" s="18" t="n">
+        <v>19</v>
+      </c>
+      <c r="D4" s="18" t="n">
+        <v>18</v>
+      </c>
+      <c r="E4" s="18" t="n">
+        <v>18</v>
+      </c>
+      <c r="F4" s="18" t="n">
+        <v>17</v>
+      </c>
+      <c r="G4" s="18" t="n">
+        <v>16</v>
+      </c>
+      <c r="H4" s="18" t="n">
+        <v>16</v>
+      </c>
+      <c r="I4" s="18" t="n">
+        <v>17</v>
+      </c>
+      <c r="J4" s="18" t="n">
+        <v>17</v>
+      </c>
+      <c r="K4" s="18" t="n">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1408,7 +2494,236 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>FORECAST ASSUMPTIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>FY26E</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>FY27E</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>FY28E</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>FY29E</t>
+        </is>
+      </c>
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t>FY30E</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Loan Growth Rate (%)</t>
+        </is>
+      </c>
+      <c r="B4" s="18" t="n">
+        <v>14</v>
+      </c>
+      <c r="C4" s="18" t="n">
+        <v>13</v>
+      </c>
+      <c r="D4" s="18" t="n">
+        <v>13</v>
+      </c>
+      <c r="E4" s="18" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" s="18" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Net Interest Margin (%)</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C5" s="18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D5" s="18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E5" s="18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F5" s="18" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>CASA Ratio (%)</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="n">
+        <v>44</v>
+      </c>
+      <c r="C6" s="18" t="n">
+        <v>45</v>
+      </c>
+      <c r="D6" s="18" t="n">
+        <v>45</v>
+      </c>
+      <c r="E6" s="18" t="n">
+        <v>46</v>
+      </c>
+      <c r="F6" s="18" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>Credit Cost (%)</t>
+        </is>
+      </c>
+      <c r="B7" s="18" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C7" s="18" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D7" s="18" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E7" s="18" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F7" s="18" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>Cost-to-Income Ratio (%)</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="n">
+        <v>41</v>
+      </c>
+      <c r="C8" s="18" t="n">
+        <v>40</v>
+      </c>
+      <c r="D8" s="18" t="n">
+        <v>39</v>
+      </c>
+      <c r="E8" s="18" t="n">
+        <v>39</v>
+      </c>
+      <c r="F8" s="18" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>Return on Assets (%)</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C9" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F9" s="18" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>Return on Equity (%)</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="C10" s="18" t="n">
+        <v>17</v>
+      </c>
+      <c r="D10" s="18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="E10" s="18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F10" s="18" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>RATIONALE</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>HDFC Bank post-merger consolidation phase stabilizing by FY26. Loan growth normalizing to 12-14% after merger integration pressures ease. NIM compression of 10-20bps over 5 years due to competitive intensity and inherited HDFC Ltd wholesale book mix normalization. CASA ratio improvement as merged entity leverages branch network and digital platforms. Credit costs remaining benign at 0.8-0.9% reflecting best-in-class underwriting and seasoned risk management. Operating leverage driving cost-to-income ratio improvement from current ~41% to ~38% as technology investments and scale benefits materialize. ROA improving to 2.0-2.1% and ROE expanding to 17-18% as profitability metrics return to pre-merger trajectory, supported by strong asset quality, operating efficiency gains, and normalized capital deployment.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1436,7 +2751,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Risk-Free Rate (Rf)</t>
         </is>
@@ -1448,7 +2763,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Equity Risk Premium</t>
         </is>
@@ -1460,7 +2775,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Beta</t>
         </is>
@@ -1472,7 +2787,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Cost of Equity (Ke)</t>
         </is>
@@ -1484,7 +2799,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Terminal Growth Rate</t>
         </is>
@@ -1496,11 +2811,11 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr"/>
+      <c r="A10" s="16" t="inlineStr"/>
       <c r="B10" s="19" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Fair Value</t>
         </is>
@@ -1519,7 +2834,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>Current Market Price</t>
         </is>
@@ -1531,7 +2846,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>RIV Fair Value</t>
         </is>
@@ -1543,7 +2858,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Target Price</t>
         </is>
@@ -1555,7 +2870,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Upside/Downside</t>
         </is>
@@ -1567,7 +2882,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Recommendation</t>
         </is>
@@ -1600,7 +2915,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1672,7 +2987,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
